--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7586,0.1129,0.1459,0.0099</t>
-  </si>
-  <si>
-    <t>0.7764,0.0591,0.1435,0.0309</t>
-  </si>
-  <si>
-    <t>0.7258,0.1264,0.1335,0.0276</t>
-  </si>
-  <si>
-    <t>0.8303,0.0433,0.1181,0.0197</t>
-  </si>
-  <si>
-    <t>0.6904,0.2356,0.0296,0.0176</t>
-  </si>
-  <si>
-    <t>0.7985,0.1005,0.0290,0.0254</t>
-  </si>
-  <si>
-    <t>0.6293,0.2933,0.0707,0.0162</t>
-  </si>
-  <si>
-    <t>0.2990,0.6528,0.1279,0.0143</t>
-  </si>
-  <si>
-    <t>0.5840,0.3342,0.0672,0.0195</t>
-  </si>
-  <si>
-    <t>0.4905,0.4080,0.0520,0.0274</t>
-  </si>
-  <si>
-    <t>0.6758,0.2532,0.0676,0.0210</t>
-  </si>
-  <si>
-    <t>0.7826,0.0873,0.0179,0.0296</t>
-  </si>
-  <si>
-    <t>0.8243,0.0647,0.0999,0.0024</t>
-  </si>
-  <si>
-    <t>0.8483,0.0161,0.2052,0.0023</t>
-  </si>
-  <si>
-    <t>0.8401,0.0231,0.2163,0.0037</t>
-  </si>
-  <si>
-    <t>0.8179,0.0108,0.3286,0.0018</t>
-  </si>
-  <si>
-    <t>0.7893,0.0645,0.1866,0.0093</t>
-  </si>
-  <si>
-    <t>0.5997,0.2903,0.0613,0.0013</t>
-  </si>
-  <si>
-    <t>0.4849,0.4879,0.0900,0.0055</t>
-  </si>
-  <si>
-    <t>0.7233,0.2112,0.0639,0.0152</t>
-  </si>
-  <si>
-    <t>0.6895,0.2433,0.0648,0.0085</t>
-  </si>
-  <si>
-    <t>0.4265,0.5819,0.0511,0.0046</t>
-  </si>
-  <si>
-    <t>0.8370,0.0252,0.2104,0.0048</t>
-  </si>
-  <si>
-    <t>0.8896,0.0068,0.1892,0.0019</t>
-  </si>
-  <si>
-    <t>0.7109,0.0123,0.4776,0.0025</t>
-  </si>
-  <si>
-    <t>0.7432,0.0465,0.2743,0.0072</t>
-  </si>
-  <si>
-    <t>0.6799,0.0254,0.4016,0.0052</t>
-  </si>
-  <si>
-    <t>0.4328,0.0213,0.6736,0.0021</t>
-  </si>
-  <si>
-    <t>0.1370,0.0066,0.9293,0.0010</t>
-  </si>
-  <si>
-    <t>0.6760,0.3158,0.0669,0.0044</t>
-  </si>
-  <si>
-    <t>0.6703,0.1934,0.1772,0.0239</t>
-  </si>
-  <si>
-    <t>0.0110,0.0770,0.9888,0.0021</t>
-  </si>
-  <si>
-    <t>0.6018,0.0976,0.2908,0.0033</t>
-  </si>
-  <si>
-    <t>0.7603,0.1617,0.1122,0.0179</t>
-  </si>
-  <si>
-    <t>0.7046,0.1417,0.1728,0.0080</t>
-  </si>
-  <si>
-    <t>0.3055,0.6851,0.0943,0.0092</t>
-  </si>
-  <si>
-    <t>0.7148,0.2015,0.1174,0.0043</t>
-  </si>
-  <si>
-    <t>0.1809,0.0919,0.7931,0.0034</t>
-  </si>
-  <si>
-    <t>0.9247,0.0024,0.1571,0.0007</t>
-  </si>
-  <si>
-    <t>0.7394,0.0042,0.4589,0.0014</t>
-  </si>
-  <si>
-    <t>0.8160,0.0062,0.2907,0.0042</t>
-  </si>
-  <si>
-    <t>0.6112,0.0139,0.6045,0.0009</t>
-  </si>
-  <si>
-    <t>0.4349,0.0943,0.3329,0.0010</t>
-  </si>
-  <si>
-    <t>0.6784,0.0060,0.5240,0.0014</t>
-  </si>
-  <si>
-    <t>0.7435,0.0556,0.2787,0.0139</t>
-  </si>
-  <si>
-    <t>0.8448,0.0500,0.1337,0.0028</t>
-  </si>
-  <si>
-    <t>0.6899,0.0850,0.2403,0.0030</t>
-  </si>
-  <si>
-    <t>0.5642,0.2199,0.1740,0.0025</t>
-  </si>
-  <si>
-    <t>0.0306,0.0154,0.9744,0.0022</t>
-  </si>
-  <si>
-    <t>0.0568,0.0065,0.9613,0.0022</t>
-  </si>
-  <si>
-    <t>0.7956,0.0154,0.3360,0.0034</t>
-  </si>
-  <si>
-    <t>0.6688,0.0218,0.4327,0.0097</t>
-  </si>
-  <si>
-    <t>0.0472,0.0074,0.9674,0.0010</t>
-  </si>
-  <si>
-    <t>0.2864,0.0174,0.8240,0.0014</t>
-  </si>
-  <si>
-    <t>0.6820,0.2657,0.0576,0.0122</t>
-  </si>
-  <si>
-    <t>0.6425,0.2820,0.0745,0.0181</t>
-  </si>
-  <si>
-    <t>0.5546,0.3645,0.1178,0.0233</t>
-  </si>
-  <si>
-    <t>0.4155,0.3218,0.3915,0.0142</t>
-  </si>
-  <si>
-    <t>0.7803,0.1322,0.0327,0.0133</t>
-  </si>
-  <si>
-    <t>0.8319,0.0995,0.0195,0.0142</t>
-  </si>
-  <si>
-    <t>0.5597,0.3975,0.0633,0.0163</t>
-  </si>
-  <si>
-    <t>0.0519,0.0575,0.9453,0.0016</t>
-  </si>
-  <si>
-    <t>0.0821,0.0407,0.9408,0.0014</t>
-  </si>
-  <si>
-    <t>0.4981,0.0066,0.6655,0.0021</t>
-  </si>
-  <si>
-    <t>0.3541,0.0254,0.7124,0.0017</t>
-  </si>
-  <si>
-    <t>0.1325,0.0022,0.9397,0.0005</t>
-  </si>
-  <si>
-    <t>0.7295,0.1290,0.1246,0.0032</t>
-  </si>
-  <si>
-    <t>0.0906,0.9083,0.0148,0.0006</t>
-  </si>
-  <si>
-    <t>0.8280,0.0669,0.1123,0.0047</t>
-  </si>
-  <si>
-    <t>0.7790,0.0811,0.1475,0.0142</t>
-  </si>
-  <si>
-    <t>0.1814,0.1491,0.7774,0.0061</t>
-  </si>
-  <si>
-    <t>0.1378,0.1035,0.6891,0.0012</t>
-  </si>
-  <si>
-    <t>0.4409,0.0183,0.6814,0.0021</t>
-  </si>
-  <si>
-    <t>0.0686,0.8111,0.1518,0.0015</t>
-  </si>
-  <si>
-    <t>0.1166,0.2039,0.7539,0.0016</t>
-  </si>
-  <si>
-    <t>0.8430,0.0308,0.1360,0.0173</t>
-  </si>
-  <si>
-    <t>0.8085,0.0599,0.1361,0.0314</t>
-  </si>
-  <si>
-    <t>0.7977,0.0279,0.1467,0.0354</t>
-  </si>
-  <si>
-    <t>0.7182,0.0692,0.2593,0.0246</t>
-  </si>
-  <si>
-    <t>0.8463,0.0202,0.0912,0.0304</t>
-  </si>
-  <si>
-    <t>0.8545,0.0222,0.1422,0.0131</t>
-  </si>
-  <si>
-    <t>0.1646,0.1031,0.7167,0.0011</t>
-  </si>
-  <si>
-    <t>0.0386,0.0401,0.9706,0.0003</t>
-  </si>
-  <si>
-    <t>0.2801,0.0181,0.7945,0.0024</t>
-  </si>
-  <si>
-    <t>0.3753,0.0118,0.7793,0.0012</t>
-  </si>
-  <si>
-    <t>0.1908,0.0720,0.7773,0.0017</t>
-  </si>
-  <si>
-    <t>0.2899,0.0513,0.6980,0.0019</t>
-  </si>
-  <si>
-    <t>0.6472,0.2432,0.0672,0.0244</t>
-  </si>
-  <si>
-    <t>0.5887,0.3355,0.0482,0.0248</t>
-  </si>
-  <si>
-    <t>0.8476,0.0653,0.0245,0.0169</t>
-  </si>
-  <si>
-    <t>0.8720,0.0728,0.0206,0.0107</t>
-  </si>
-  <si>
-    <t>0.6401,0.2777,0.0605,0.0154</t>
-  </si>
-  <si>
-    <t>0.5911,0.2110,0.0450,0.0527</t>
-  </si>
-  <si>
-    <t>0.7322,0.1792,0.0381,0.0143</t>
-  </si>
-  <si>
-    <t>0.4573,0.5151,0.0715,0.0131</t>
-  </si>
-  <si>
-    <t>0.5733,0.2429,0.0345,0.0353</t>
-  </si>
-  <si>
-    <t>0.5683,0.3926,0.0780,0.0181</t>
-  </si>
-  <si>
-    <t>0.7303,0.1705,0.0368,0.0204</t>
-  </si>
-  <si>
-    <t>0.7842,0.1080,0.0161,0.0224</t>
-  </si>
-  <si>
-    <t>0.8545,0.0708,0.0134,0.0134</t>
-  </si>
-  <si>
-    <t>0.8380,0.1096,0.0174,0.0101</t>
-  </si>
-  <si>
-    <t>0.4671,0.4323,0.1583,0.0370</t>
-  </si>
-  <si>
-    <t>0.7389,0.1228,0.0736,0.0518</t>
-  </si>
-  <si>
-    <t>0.6747,0.0215,0.4593,0.0077</t>
-  </si>
-  <si>
-    <t>0.6737,0.0205,0.4624,0.0021</t>
-  </si>
-  <si>
-    <t>0.8902,0.0153,0.1521,0.0036</t>
-  </si>
-  <si>
-    <t>0.7888,0.0215,0.3035,0.0038</t>
-  </si>
-  <si>
-    <t>0.2987,0.7108,0.0764,0.0078</t>
-  </si>
-  <si>
-    <t>0.3994,0.5278,0.1363,0.0148</t>
-  </si>
-  <si>
-    <t>0.4722,0.4745,0.0980,0.0137</t>
-  </si>
-  <si>
-    <t>0.7580,0.1714,0.0545,0.0115</t>
-  </si>
-  <si>
-    <t>0.3000,0.6381,0.1311,0.0092</t>
-  </si>
-  <si>
-    <t>0.6979,0.2431,0.0567,0.0047</t>
-  </si>
-  <si>
-    <t>0.5891,0.3443,0.1180,0.0112</t>
-  </si>
-  <si>
-    <t>0.7727,0.0589,0.1857,0.0296</t>
-  </si>
-  <si>
-    <t>0.8720,0.0127,0.2096,0.0023</t>
-  </si>
-  <si>
-    <t>0.8601,0.0298,0.1523,0.0087</t>
-  </si>
-  <si>
-    <t>0.7045,0.0464,0.3695,0.0056</t>
-  </si>
-  <si>
-    <t>0.8025,0.0711,0.1414,0.0125</t>
-  </si>
-  <si>
-    <t>0.6436,0.1330,0.2107,0.0027</t>
-  </si>
-  <si>
-    <t>0.5339,0.2511,0.1592,0.0027</t>
-  </si>
-  <si>
-    <t>0.3176,0.4889,0.2228,0.0054</t>
-  </si>
-  <si>
-    <t>0.2456,0.4573,0.1371,0.0015</t>
-  </si>
-  <si>
-    <t>0.5965,0.3673,0.0651,0.0021</t>
-  </si>
-  <si>
-    <t>0.3975,0.5027,0.1824,0.0146</t>
-  </si>
-  <si>
-    <t>0.6820,0.2310,0.1076,0.0128</t>
-  </si>
-  <si>
-    <t>0.7699,0.1761,0.0486,0.0101</t>
-  </si>
-  <si>
-    <t>0.7463,0.1695,0.0341,0.0148</t>
-  </si>
-  <si>
-    <t>0.6226,0.2808,0.0642,0.0236</t>
-  </si>
-  <si>
-    <t>0.7042,0.2069,0.0896,0.0324</t>
-  </si>
-  <si>
-    <t>0.5783,0.2920,0.1999,0.0156</t>
-  </si>
-  <si>
-    <t>0.6134,0.3116,0.1385,0.0126</t>
-  </si>
-  <si>
-    <t>0.5455,0.3799,0.0640,0.0231</t>
-  </si>
-  <si>
-    <t>0.6845,0.1990,0.0598,0.0383</t>
-  </si>
-  <si>
-    <t>0.4042,0.0223,0.7242,0.0021</t>
-  </si>
-  <si>
-    <t>0.1919,0.0171,0.8886,0.0008</t>
-  </si>
-  <si>
-    <t>0.1426,0.0044,0.9302,0.0005</t>
-  </si>
-  <si>
-    <t>0.6154,0.0128,0.5955,0.0023</t>
-  </si>
-  <si>
-    <t>0.9154,0.0135,0.1060,0.0040</t>
-  </si>
-  <si>
-    <t>0.8944,0.0112,0.1630,0.0030</t>
-  </si>
-  <si>
-    <t>0.8160,0.0382,0.1938,0.0048</t>
-  </si>
-  <si>
-    <t>0.8306,0.0383,0.1620,0.0048</t>
-  </si>
-  <si>
-    <t>0.8253,0.0388,0.1867,0.0104</t>
-  </si>
-  <si>
-    <t>0.8428,0.0144,0.0522,0.0521</t>
-  </si>
-  <si>
-    <t>0.7306,0.0324,0.2365,0.0409</t>
-  </si>
-  <si>
-    <t>0.8596,0.0187,0.1028,0.0206</t>
-  </si>
-  <si>
-    <t>0.1489,0.2104,0.7236,0.0075</t>
-  </si>
-  <si>
-    <t>0.7532,0.1130,0.0262,0.0253</t>
-  </si>
-  <si>
-    <t>0.7927,0.1273,0.0740,0.0132</t>
-  </si>
-  <si>
-    <t>0.8715,0.0601,0.0124,0.0143</t>
-  </si>
-  <si>
-    <t>0.7211,0.1839,0.0508,0.0196</t>
-  </si>
-  <si>
-    <t>0.8736,0.0567,0.0385,0.0120</t>
-  </si>
-  <si>
-    <t>0.6353,0.1692,0.2396,0.0478</t>
-  </si>
-  <si>
-    <t>0.6239,0.2570,0.0719,0.0333</t>
-  </si>
-  <si>
-    <t>0.1273,0.1338,0.8818,0.0091</t>
-  </si>
-  <si>
-    <t>0.7623,0.1023,0.0740,0.0370</t>
-  </si>
-  <si>
-    <t>0.6154,0.1706,0.0902,0.0812</t>
-  </si>
-  <si>
-    <t>0.7037,0.1900,0.1269,0.0113</t>
-  </si>
-  <si>
-    <t>0.6534,0.2170,0.1116,0.0221</t>
-  </si>
-  <si>
-    <t>0.6755,0.2638,0.0853,0.0143</t>
-  </si>
-  <si>
-    <t>0.6983,0.1857,0.1081,0.0086</t>
-  </si>
-  <si>
-    <t>0.8209,0.0781,0.0912,0.0096</t>
-  </si>
-  <si>
-    <t>0.9124,0.0358,0.0400,0.0057</t>
-  </si>
-  <si>
-    <t>0.7063,0.1949,0.0398,0.0229</t>
-  </si>
-  <si>
-    <t>0.8573,0.0823,0.0409,0.0168</t>
-  </si>
-  <si>
-    <t>0.6506,0.2740,0.0800,0.0263</t>
-  </si>
-  <si>
-    <t>0.7248,0.1181,0.0238,0.0426</t>
-  </si>
-  <si>
-    <t>0.8221,0.1123,0.0275,0.0140</t>
-  </si>
-  <si>
-    <t>0.7232,0.1906,0.0781,0.0165</t>
-  </si>
-  <si>
-    <t>0.6945,0.2004,0.0315,0.0247</t>
-  </si>
-  <si>
-    <t>0.7181,0.2207,0.0557,0.0116</t>
-  </si>
-  <si>
-    <t>0.6907,0.2227,0.0760,0.0089</t>
-  </si>
-  <si>
-    <t>0.6547,0.3513,0.0394,0.0050</t>
-  </si>
-  <si>
-    <t>0.5140,0.4074,0.1325,0.0174</t>
-  </si>
-  <si>
-    <t>0.7795,0.0958,0.1122,0.0154</t>
-  </si>
-  <si>
-    <t>0.7149,0.1647,0.0281,0.0191</t>
-  </si>
-  <si>
-    <t>0.5195,0.3947,0.1222,0.0154</t>
-  </si>
-  <si>
-    <t>0.7777,0.1513,0.0213,0.0112</t>
-  </si>
-  <si>
-    <t>0.6415,0.2887,0.1130,0.0194</t>
-  </si>
-  <si>
-    <t>0.0219,0.0578,0.9735,0.0004</t>
-  </si>
-  <si>
-    <t>0.7460,0.1295,0.0837,0.0317</t>
-  </si>
-  <si>
-    <t>0.2167,0.0108,0.8610,0.0021</t>
-  </si>
-  <si>
-    <t>0.3459,0.0161,0.7728,0.0022</t>
-  </si>
-  <si>
-    <t>0.8150,0.0354,0.2286,0.0046</t>
-  </si>
-  <si>
-    <t>0.1977,0.0307,0.8783,0.0017</t>
-  </si>
-  <si>
-    <t>0.6195,0.0220,0.5181,0.0046</t>
-  </si>
-  <si>
-    <t>0.4011,0.0131,0.7571,0.0014</t>
-  </si>
-  <si>
-    <t>0.2144,0.0243,0.8592,0.0023</t>
-  </si>
-  <si>
-    <t>0.7507,0.0462,0.2800,0.0070</t>
-  </si>
-  <si>
-    <t>0.6470,0.0291,0.4720,0.0036</t>
-  </si>
-  <si>
-    <t>0.5357,0.1527,0.3570,0.0099</t>
-  </si>
-  <si>
-    <t>0.6538,0.0795,0.3522,0.0076</t>
-  </si>
-  <si>
-    <t>0.6943,0.1196,0.1745,0.0069</t>
-  </si>
-  <si>
-    <t>0.8138,0.0252,0.2431,0.0017</t>
-  </si>
-  <si>
-    <t>0.8470,0.0235,0.1893,0.0047</t>
-  </si>
-  <si>
-    <t>0.6932,0.1095,0.2139,0.0111</t>
-  </si>
-  <si>
-    <t>0.3354,0.6540,0.1110,0.0121</t>
-  </si>
-  <si>
-    <t>0.4059,0.5561,0.0601,0.0130</t>
-  </si>
-  <si>
-    <t>0.4473,0.4628,0.2291,0.0304</t>
-  </si>
-  <si>
-    <t>0.4575,0.5294,0.0840,0.0118</t>
-  </si>
-  <si>
-    <t>0.7522,0.1426,0.0609,0.0246</t>
-  </si>
-  <si>
-    <t>0.8840,0.0170,0.1471,0.0039</t>
-  </si>
-  <si>
-    <t>0.8744,0.0222,0.1538,0.0028</t>
-  </si>
-  <si>
-    <t>0.7961,0.0449,0.1929,0.0057</t>
-  </si>
-  <si>
-    <t>0.8251,0.0454,0.1550,0.0064</t>
-  </si>
-  <si>
-    <t>0.8484,0.0449,0.1438,0.0096</t>
-  </si>
-  <si>
-    <t>0.0343,0.0377,0.9538,0.0005</t>
-  </si>
-  <si>
-    <t>0.8591,0.0064,0.2343,0.0039</t>
-  </si>
-  <si>
-    <t>0.6241,0.0071,0.5517,0.0025</t>
-  </si>
-  <si>
-    <t>0.7363,0.0040,0.5237,0.0006</t>
-  </si>
-  <si>
-    <t>0.7937,0.0047,0.3671,0.0015</t>
-  </si>
-  <si>
-    <t>0.6878,0.2544,0.0511,0.0136</t>
-  </si>
-  <si>
-    <t>0.7155,0.2351,0.0687,0.0098</t>
-  </si>
-  <si>
-    <t>0.6849,0.2008,0.0373,0.0227</t>
-  </si>
-  <si>
-    <t>0.6648,0.2137,0.0302,0.0231</t>
-  </si>
-  <si>
-    <t>0.5383,0.3426,0.1232,0.0380</t>
-  </si>
-  <si>
-    <t>0.7031,0.1968,0.0422,0.0185</t>
-  </si>
-  <si>
-    <t>0.6125,0.3013,0.0391,0.0176</t>
-  </si>
-  <si>
-    <t>0.6512,0.2628,0.1004,0.0223</t>
-  </si>
-  <si>
-    <t>0.6463,0.0902,0.3336,0.0049</t>
-  </si>
-  <si>
-    <t>0.5776,0.2671,0.1946,0.0143</t>
-  </si>
-  <si>
-    <t>0.7092,0.1481,0.1651,0.0104</t>
-  </si>
-  <si>
-    <t>0.0691,0.0087,0.9664,0.0003</t>
-  </si>
-  <si>
-    <t>0.0224,0.0119,0.9776,0.0011</t>
-  </si>
-  <si>
-    <t>0.3458,0.0584,0.7205,0.0052</t>
-  </si>
-  <si>
-    <t>0.0194,0.0008,0.9920,0.0002</t>
-  </si>
-  <si>
-    <t>0.5831,0.0073,0.6430,0.0010</t>
-  </si>
-  <si>
-    <t>0.0077,0.0112,0.9915,0.0008</t>
-  </si>
-  <si>
-    <t>0.6113,0.0054,0.6026,0.0016</t>
-  </si>
-  <si>
-    <t>0.8379,0.0203,0.2119,0.0065</t>
-  </si>
-  <si>
-    <t>0.8252,0.0231,0.2472,0.0035</t>
-  </si>
-  <si>
-    <t>0.8468,0.0273,0.1681,0.0032</t>
-  </si>
-  <si>
-    <t>0.8136,0.0638,0.1506,0.0079</t>
-  </si>
-  <si>
-    <t>0.3636,0.6096,0.1109,0.0093</t>
-  </si>
-  <si>
-    <t>0.7537,0.1338,0.0261,0.0212</t>
-  </si>
-  <si>
-    <t>0.7636,0.1398,0.0282,0.0193</t>
-  </si>
-  <si>
-    <t>0.6304,0.2846,0.0656,0.0270</t>
-  </si>
-  <si>
-    <t>0.5179,0.4168,0.1125,0.0177</t>
-  </si>
-  <si>
-    <t>0.7060,0.2059,0.0431,0.0205</t>
-  </si>
-  <si>
-    <t>0.5190,0.4259,0.1046,0.0202</t>
-  </si>
-  <si>
-    <t>0.7631,0.1460,0.0333,0.0235</t>
-  </si>
-  <si>
-    <t>0.5278,0.0180,0.6063,0.0015</t>
-  </si>
-  <si>
-    <t>0.0654,0.0277,0.9582,0.0007</t>
-  </si>
-  <si>
-    <t>0.1359,0.0206,0.9108,0.0022</t>
-  </si>
-  <si>
-    <t>0.9343,0.0070,0.0861,0.0023</t>
-  </si>
-  <si>
-    <t>0.3205,0.0076,0.8135,0.0013</t>
-  </si>
-  <si>
-    <t>0.7283,0.0220,0.3802,0.0044</t>
-  </si>
-  <si>
-    <t>0.6287,0.0174,0.5282,0.0038</t>
-  </si>
-  <si>
-    <t>0.8508,0.0019,0.2775,0.0019</t>
-  </si>
-  <si>
-    <t>0.8080,0.0761,0.0853,0.0149</t>
-  </si>
-  <si>
-    <t>0.7405,0.0462,0.3086,0.0179</t>
-  </si>
-  <si>
-    <t>0.7858,0.0450,0.1438,0.0398</t>
-  </si>
-  <si>
-    <t>0.8139,0.0298,0.0726,0.0502</t>
-  </si>
-  <si>
-    <t>0.8354,0.0381,0.1493,0.0135</t>
-  </si>
-  <si>
-    <t>0.6486,0.0936,0.3195,0.0197</t>
+    <t>0.7556,0.0875,0.1822,0.0088</t>
+  </si>
+  <si>
+    <t>0.6782,0.1016,0.2964,0.0396</t>
+  </si>
+  <si>
+    <t>0.6053,0.2495,0.1656,0.0189</t>
+  </si>
+  <si>
+    <t>0.7961,0.0613,0.1111,0.0356</t>
+  </si>
+  <si>
+    <t>0.6247,0.2503,0.0648,0.0428</t>
+  </si>
+  <si>
+    <t>0.7779,0.1253,0.0330,0.0220</t>
+  </si>
+  <si>
+    <t>0.6902,0.2021,0.0898,0.0229</t>
+  </si>
+  <si>
+    <t>0.7128,0.2137,0.0418,0.0135</t>
+  </si>
+  <si>
+    <t>0.5937,0.3569,0.0749,0.0126</t>
+  </si>
+  <si>
+    <t>0.4814,0.4878,0.1098,0.0103</t>
+  </si>
+  <si>
+    <t>0.8214,0.0920,0.0286,0.0270</t>
+  </si>
+  <si>
+    <t>0.6986,0.2426,0.0393,0.0171</t>
+  </si>
+  <si>
+    <t>0.7860,0.0252,0.3023,0.0023</t>
+  </si>
+  <si>
+    <t>0.7821,0.0377,0.2400,0.0025</t>
+  </si>
+  <si>
+    <t>0.7506,0.0351,0.3154,0.0086</t>
+  </si>
+  <si>
+    <t>0.7667,0.0245,0.3356,0.0024</t>
+  </si>
+  <si>
+    <t>0.7226,0.1176,0.1585,0.0151</t>
+  </si>
+  <si>
+    <t>0.6357,0.2721,0.1051,0.0045</t>
+  </si>
+  <si>
+    <t>0.6464,0.2900,0.0761,0.0032</t>
+  </si>
+  <si>
+    <t>0.6377,0.2832,0.1075,0.0048</t>
+  </si>
+  <si>
+    <t>0.2399,0.6822,0.1075,0.0040</t>
+  </si>
+  <si>
+    <t>0.6173,0.3179,0.0606,0.0040</t>
+  </si>
+  <si>
+    <t>0.8585,0.0210,0.1816,0.0035</t>
+  </si>
+  <si>
+    <t>0.7347,0.0081,0.4433,0.0019</t>
+  </si>
+  <si>
+    <t>0.8392,0.0028,0.3401,0.0010</t>
+  </si>
+  <si>
+    <t>0.6510,0.0215,0.4651,0.0084</t>
+  </si>
+  <si>
+    <t>0.6755,0.0184,0.4488,0.0035</t>
+  </si>
+  <si>
+    <t>0.7303,0.0084,0.4641,0.0015</t>
+  </si>
+  <si>
+    <t>0.3512,0.0111,0.7956,0.0018</t>
+  </si>
+  <si>
+    <t>0.8273,0.0886,0.1020,0.0067</t>
+  </si>
+  <si>
+    <t>0.5998,0.2790,0.1025,0.0272</t>
+  </si>
+  <si>
+    <t>0.0386,0.2900,0.9465,0.0065</t>
+  </si>
+  <si>
+    <t>0.5388,0.1605,0.3086,0.0035</t>
+  </si>
+  <si>
+    <t>0.6139,0.2091,0.2036,0.0216</t>
+  </si>
+  <si>
+    <t>0.7230,0.1236,0.1803,0.0150</t>
+  </si>
+  <si>
+    <t>0.9091,0.0397,0.0127,0.0092</t>
+  </si>
+  <si>
+    <t>0.8303,0.0874,0.0918,0.0030</t>
+  </si>
+  <si>
+    <t>0.4344,0.0603,0.5149,0.0043</t>
+  </si>
+  <si>
+    <t>0.1708,0.0085,0.8979,0.0017</t>
+  </si>
+  <si>
+    <t>0.5338,0.0193,0.6206,0.0009</t>
+  </si>
+  <si>
+    <t>0.8003,0.0061,0.3338,0.0023</t>
+  </si>
+  <si>
+    <t>0.5293,0.0055,0.7125,0.0008</t>
+  </si>
+  <si>
+    <t>0.4340,0.0319,0.5294,0.0018</t>
+  </si>
+  <si>
+    <t>0.6776,0.0076,0.5118,0.0017</t>
+  </si>
+  <si>
+    <t>0.8634,0.0352,0.0886,0.0179</t>
+  </si>
+  <si>
+    <t>0.7734,0.0673,0.1500,0.0013</t>
+  </si>
+  <si>
+    <t>0.6084,0.0685,0.3356,0.0012</t>
+  </si>
+  <si>
+    <t>0.7039,0.2005,0.0730,0.0014</t>
+  </si>
+  <si>
+    <t>0.0356,0.0535,0.9580,0.0039</t>
+  </si>
+  <si>
+    <t>0.0736,0.0070,0.9674,0.0005</t>
+  </si>
+  <si>
+    <t>0.7806,0.0232,0.3318,0.0033</t>
+  </si>
+  <si>
+    <t>0.6990,0.0141,0.4807,0.0021</t>
+  </si>
+  <si>
+    <t>0.0490,0.0061,0.9710,0.0005</t>
+  </si>
+  <si>
+    <t>0.2742,0.0118,0.8542,0.0011</t>
+  </si>
+  <si>
+    <t>0.7716,0.1723,0.0343,0.0098</t>
+  </si>
+  <si>
+    <t>0.7712,0.1286,0.0322,0.0243</t>
+  </si>
+  <si>
+    <t>0.6465,0.2675,0.0600,0.0290</t>
+  </si>
+  <si>
+    <t>0.4222,0.2782,0.5133,0.0219</t>
+  </si>
+  <si>
+    <t>0.7295,0.1750,0.0464,0.0304</t>
+  </si>
+  <si>
+    <t>0.7124,0.2036,0.0310,0.0164</t>
+  </si>
+  <si>
+    <t>0.5393,0.3983,0.0450,0.0135</t>
+  </si>
+  <si>
+    <t>0.0249,0.1816,0.9527,0.0012</t>
+  </si>
+  <si>
+    <t>0.0713,0.0111,0.9635,0.0007</t>
+  </si>
+  <si>
+    <t>0.2494,0.0263,0.7922,0.0035</t>
+  </si>
+  <si>
+    <t>0.1165,0.0567,0.8902,0.0020</t>
+  </si>
+  <si>
+    <t>0.0468,0.0120,0.9728,0.0006</t>
+  </si>
+  <si>
+    <t>0.6143,0.1853,0.1587,0.0022</t>
+  </si>
+  <si>
+    <t>0.0309,0.9683,0.0064,0.0005</t>
+  </si>
+  <si>
+    <t>0.7087,0.1847,0.1392,0.0101</t>
+  </si>
+  <si>
+    <t>0.7484,0.1625,0.0934,0.0092</t>
+  </si>
+  <si>
+    <t>0.1708,0.3516,0.6884,0.0145</t>
+  </si>
+  <si>
+    <t>0.2638,0.0587,0.6817,0.0013</t>
+  </si>
+  <si>
+    <t>0.4688,0.0342,0.6319,0.0014</t>
+  </si>
+  <si>
+    <t>0.1139,0.3749,0.3380,0.0011</t>
+  </si>
+  <si>
+    <t>0.0944,0.1535,0.7773,0.0012</t>
+  </si>
+  <si>
+    <t>0.9029,0.0077,0.0482,0.0176</t>
+  </si>
+  <si>
+    <t>0.8326,0.0348,0.0768,0.0536</t>
+  </si>
+  <si>
+    <t>0.7595,0.0223,0.1742,0.0556</t>
+  </si>
+  <si>
+    <t>0.8692,0.0222,0.0718,0.0233</t>
+  </si>
+  <si>
+    <t>0.7715,0.0769,0.2178,0.0153</t>
+  </si>
+  <si>
+    <t>0.7877,0.0457,0.2086,0.0198</t>
+  </si>
+  <si>
+    <t>0.1404,0.0938,0.7670,0.0013</t>
+  </si>
+  <si>
+    <t>0.0295,0.0667,0.9667,0.0003</t>
+  </si>
+  <si>
+    <t>0.3307,0.0194,0.7825,0.0023</t>
+  </si>
+  <si>
+    <t>0.5174,0.0290,0.5973,0.0035</t>
+  </si>
+  <si>
+    <t>0.0668,0.3156,0.6229,0.0008</t>
+  </si>
+  <si>
+    <t>0.2865,0.0374,0.7313,0.0011</t>
+  </si>
+  <si>
+    <t>0.4306,0.4778,0.1444,0.0318</t>
+  </si>
+  <si>
+    <t>0.6054,0.3472,0.0696,0.0109</t>
+  </si>
+  <si>
+    <t>0.5634,0.4038,0.1016,0.0136</t>
+  </si>
+  <si>
+    <t>0.5589,0.3119,0.0930,0.0371</t>
+  </si>
+  <si>
+    <t>0.7955,0.1420,0.0278,0.0108</t>
+  </si>
+  <si>
+    <t>0.6126,0.2700,0.0414,0.0233</t>
+  </si>
+  <si>
+    <t>0.5217,0.4191,0.0788,0.0165</t>
+  </si>
+  <si>
+    <t>0.5262,0.4245,0.0906,0.0175</t>
+  </si>
+  <si>
+    <t>0.6102,0.2884,0.0584,0.0214</t>
+  </si>
+  <si>
+    <t>0.4712,0.4766,0.0866,0.0164</t>
+  </si>
+  <si>
+    <t>0.5944,0.3549,0.0766,0.0186</t>
+  </si>
+  <si>
+    <t>0.6392,0.2236,0.0343,0.0277</t>
+  </si>
+  <si>
+    <t>0.8525,0.0634,0.0202,0.0224</t>
+  </si>
+  <si>
+    <t>0.7159,0.2036,0.0445,0.0154</t>
+  </si>
+  <si>
+    <t>0.8093,0.1189,0.0199,0.0145</t>
+  </si>
+  <si>
+    <t>0.5683,0.3669,0.0787,0.0239</t>
+  </si>
+  <si>
+    <t>0.3247,0.0195,0.7758,0.0025</t>
+  </si>
+  <si>
+    <t>0.6748,0.0196,0.4653,0.0022</t>
+  </si>
+  <si>
+    <t>0.7257,0.0136,0.3956,0.0057</t>
+  </si>
+  <si>
+    <t>0.4528,0.0153,0.7004,0.0030</t>
+  </si>
+  <si>
+    <t>0.2594,0.6177,0.1726,0.0082</t>
+  </si>
+  <si>
+    <t>0.6026,0.3697,0.0699,0.0075</t>
+  </si>
+  <si>
+    <t>0.7877,0.1598,0.0673,0.0050</t>
+  </si>
+  <si>
+    <t>0.5178,0.4538,0.0987,0.0065</t>
+  </si>
+  <si>
+    <t>0.4724,0.4832,0.0999,0.0141</t>
+  </si>
+  <si>
+    <t>0.2983,0.6490,0.1070,0.0058</t>
+  </si>
+  <si>
+    <t>0.6415,0.2994,0.0971,0.0112</t>
+  </si>
+  <si>
+    <t>0.7872,0.0498,0.1980,0.0114</t>
+  </si>
+  <si>
+    <t>0.7747,0.0498,0.2309,0.0073</t>
+  </si>
+  <si>
+    <t>0.8249,0.0306,0.2277,0.0058</t>
+  </si>
+  <si>
+    <t>0.7685,0.0476,0.2651,0.0069</t>
+  </si>
+  <si>
+    <t>0.7916,0.0653,0.1512,0.0113</t>
+  </si>
+  <si>
+    <t>0.5203,0.3064,0.1475,0.0051</t>
+  </si>
+  <si>
+    <t>0.3779,0.3655,0.1818,0.0029</t>
+  </si>
+  <si>
+    <t>0.6637,0.2158,0.1200,0.0090</t>
+  </si>
+  <si>
+    <t>0.1433,0.6795,0.1775,0.0019</t>
+  </si>
+  <si>
+    <t>0.4560,0.4542,0.1159,0.0031</t>
+  </si>
+  <si>
+    <t>0.7111,0.2269,0.0406,0.0082</t>
+  </si>
+  <si>
+    <t>0.4988,0.4334,0.1159,0.0150</t>
+  </si>
+  <si>
+    <t>0.7757,0.1322,0.0395,0.0181</t>
+  </si>
+  <si>
+    <t>0.7893,0.0936,0.0257,0.0262</t>
+  </si>
+  <si>
+    <t>0.6824,0.2056,0.0758,0.0305</t>
+  </si>
+  <si>
+    <t>0.4880,0.4374,0.1381,0.0137</t>
+  </si>
+  <si>
+    <t>0.7441,0.2076,0.0371,0.0146</t>
+  </si>
+  <si>
+    <t>0.7992,0.1308,0.0881,0.0100</t>
+  </si>
+  <si>
+    <t>0.7587,0.1164,0.0293,0.0326</t>
+  </si>
+  <si>
+    <t>0.6966,0.2033,0.0317,0.0229</t>
+  </si>
+  <si>
+    <t>0.3465,0.0086,0.8082,0.0014</t>
+  </si>
+  <si>
+    <t>0.4475,0.0096,0.7381,0.0009</t>
+  </si>
+  <si>
+    <t>0.1437,0.0055,0.9256,0.0012</t>
+  </si>
+  <si>
+    <t>0.5428,0.0269,0.5696,0.0016</t>
+  </si>
+  <si>
+    <t>0.8382,0.0381,0.1556,0.0048</t>
+  </si>
+  <si>
+    <t>0.7868,0.0380,0.2740,0.0072</t>
+  </si>
+  <si>
+    <t>0.7220,0.0645,0.2919,0.0114</t>
+  </si>
+  <si>
+    <t>0.8839,0.0269,0.0838,0.0074</t>
+  </si>
+  <si>
+    <t>0.8230,0.0428,0.0986,0.0328</t>
+  </si>
+  <si>
+    <t>0.7218,0.0197,0.1913,0.0673</t>
+  </si>
+  <si>
+    <t>0.8418,0.0171,0.1064,0.0337</t>
+  </si>
+  <si>
+    <t>0.8539,0.0142,0.0895,0.0297</t>
+  </si>
+  <si>
+    <t>0.2053,0.1595,0.6235,0.0042</t>
+  </si>
+  <si>
+    <t>0.7742,0.1419,0.0369,0.0140</t>
+  </si>
+  <si>
+    <t>0.8620,0.0574,0.0306,0.0126</t>
+  </si>
+  <si>
+    <t>0.7019,0.2413,0.0487,0.0160</t>
+  </si>
+  <si>
+    <t>0.7483,0.1734,0.0925,0.0184</t>
+  </si>
+  <si>
+    <t>0.5698,0.3473,0.1355,0.0186</t>
+  </si>
+  <si>
+    <t>0.7112,0.1634,0.0955,0.0164</t>
+  </si>
+  <si>
+    <t>0.7323,0.1424,0.1003,0.0362</t>
+  </si>
+  <si>
+    <t>0.0962,0.0480,0.8964,0.0183</t>
+  </si>
+  <si>
+    <t>0.7790,0.0818,0.0873,0.0270</t>
+  </si>
+  <si>
+    <t>0.7251,0.1892,0.0562,0.0209</t>
+  </si>
+  <si>
+    <t>0.8274,0.0688,0.1059,0.0049</t>
+  </si>
+  <si>
+    <t>0.8106,0.0702,0.1179,0.0104</t>
+  </si>
+  <si>
+    <t>0.6443,0.2587,0.1295,0.0075</t>
+  </si>
+  <si>
+    <t>0.7971,0.0550,0.2091,0.0085</t>
+  </si>
+  <si>
+    <t>0.8040,0.1252,0.0746,0.0040</t>
+  </si>
+  <si>
+    <t>0.8728,0.0985,0.0235,0.0042</t>
+  </si>
+  <si>
+    <t>0.6635,0.2383,0.1272,0.0199</t>
+  </si>
+  <si>
+    <t>0.6178,0.2493,0.1026,0.0322</t>
+  </si>
+  <si>
+    <t>0.5693,0.3328,0.0640,0.0190</t>
+  </si>
+  <si>
+    <t>0.7613,0.1356,0.0236,0.0203</t>
+  </si>
+  <si>
+    <t>0.6545,0.2884,0.1082,0.0237</t>
+  </si>
+  <si>
+    <t>0.7412,0.1754,0.0343,0.0209</t>
+  </si>
+  <si>
+    <t>0.9438,0.0243,0.0079,0.0053</t>
+  </si>
+  <si>
+    <t>0.7484,0.1458,0.0522,0.0324</t>
+  </si>
+  <si>
+    <t>0.6860,0.2350,0.0772,0.0115</t>
+  </si>
+  <si>
+    <t>0.5377,0.4279,0.1147,0.0126</t>
+  </si>
+  <si>
+    <t>0.5410,0.4007,0.0869,0.0125</t>
+  </si>
+  <si>
+    <t>0.6756,0.1889,0.1710,0.0150</t>
+  </si>
+  <si>
+    <t>0.5904,0.3753,0.0803,0.0091</t>
+  </si>
+  <si>
+    <t>0.6926,0.1977,0.1113,0.0210</t>
+  </si>
+  <si>
+    <t>0.6232,0.3365,0.0450,0.0119</t>
+  </si>
+  <si>
+    <t>0.6397,0.2477,0.0616,0.0159</t>
+  </si>
+  <si>
+    <t>0.0188,0.2041,0.9518,0.0017</t>
+  </si>
+  <si>
+    <t>0.3567,0.5517,0.1943,0.0152</t>
+  </si>
+  <si>
+    <t>0.4077,0.0136,0.7196,0.0026</t>
+  </si>
+  <si>
+    <t>0.6671,0.0176,0.4821,0.0050</t>
+  </si>
+  <si>
+    <t>0.4085,0.0484,0.6494,0.0035</t>
+  </si>
+  <si>
+    <t>0.0190,0.0168,0.9913,0.0004</t>
+  </si>
+  <si>
+    <t>0.5465,0.0189,0.6198,0.0032</t>
+  </si>
+  <si>
+    <t>0.6367,0.0062,0.5713,0.0015</t>
+  </si>
+  <si>
+    <t>0.2423,0.0180,0.8398,0.0016</t>
+  </si>
+  <si>
+    <t>0.6939,0.0490,0.3685,0.0107</t>
+  </si>
+  <si>
+    <t>0.7122,0.0354,0.3738,0.0049</t>
+  </si>
+  <si>
+    <t>0.8078,0.0882,0.0979,0.0033</t>
+  </si>
+  <si>
+    <t>0.5420,0.1782,0.3228,0.0086</t>
+  </si>
+  <si>
+    <t>0.7297,0.0519,0.3069,0.0078</t>
+  </si>
+  <si>
+    <t>0.7992,0.0308,0.2659,0.0045</t>
+  </si>
+  <si>
+    <t>0.7938,0.0479,0.1974,0.0094</t>
+  </si>
+  <si>
+    <t>0.7954,0.0501,0.1844,0.0068</t>
+  </si>
+  <si>
+    <t>0.6204,0.3349,0.0624,0.0061</t>
+  </si>
+  <si>
+    <t>0.6479,0.3073,0.0850,0.0090</t>
+  </si>
+  <si>
+    <t>0.5336,0.3701,0.1259,0.0261</t>
+  </si>
+  <si>
+    <t>0.6829,0.2277,0.0449,0.0174</t>
+  </si>
+  <si>
+    <t>0.7422,0.2126,0.0324,0.0094</t>
+  </si>
+  <si>
+    <t>0.8166,0.0573,0.1390,0.0057</t>
+  </si>
+  <si>
+    <t>0.8269,0.0331,0.1763,0.0041</t>
+  </si>
+  <si>
+    <t>0.8561,0.0307,0.1417,0.0046</t>
+  </si>
+  <si>
+    <t>0.8903,0.0133,0.1336,0.0040</t>
+  </si>
+  <si>
+    <t>0.7985,0.0393,0.2076,0.0226</t>
+  </si>
+  <si>
+    <t>0.0803,0.0500,0.9366,0.0030</t>
+  </si>
+  <si>
+    <t>0.8206,0.0056,0.3152,0.0029</t>
+  </si>
+  <si>
+    <t>0.8425,0.0072,0.2787,0.0026</t>
+  </si>
+  <si>
+    <t>0.5820,0.0125,0.5099,0.0074</t>
+  </si>
+  <si>
+    <t>0.6409,0.0111,0.5195,0.0022</t>
+  </si>
+  <si>
+    <t>0.4916,0.4646,0.0831,0.0199</t>
+  </si>
+  <si>
+    <t>0.4553,0.4966,0.0917,0.0161</t>
+  </si>
+  <si>
+    <t>0.8036,0.1317,0.0618,0.0147</t>
+  </si>
+  <si>
+    <t>0.5614,0.3726,0.0517,0.0207</t>
+  </si>
+  <si>
+    <t>0.6101,0.3063,0.0564,0.0211</t>
+  </si>
+  <si>
+    <t>0.7473,0.1821,0.0214,0.0207</t>
+  </si>
+  <si>
+    <t>0.5574,0.4118,0.0502,0.0113</t>
+  </si>
+  <si>
+    <t>0.6465,0.2550,0.0442,0.0142</t>
+  </si>
+  <si>
+    <t>0.6348,0.0946,0.3651,0.0095</t>
+  </si>
+  <si>
+    <t>0.6791,0.2142,0.1213,0.0061</t>
+  </si>
+  <si>
+    <t>0.6528,0.2668,0.1322,0.0146</t>
+  </si>
+  <si>
+    <t>0.0398,0.0074,0.9801,0.0006</t>
+  </si>
+  <si>
+    <t>0.0223,0.0078,0.9820,0.0014</t>
+  </si>
+  <si>
+    <t>0.5155,0.0165,0.6322,0.0029</t>
+  </si>
+  <si>
+    <t>0.0461,0.0101,0.9723,0.0012</t>
+  </si>
+  <si>
+    <t>0.2712,0.0102,0.8503,0.0011</t>
+  </si>
+  <si>
+    <t>0.0067,0.0082,0.9936,0.0007</t>
+  </si>
+  <si>
+    <t>0.3699,0.0152,0.7833,0.0016</t>
+  </si>
+  <si>
+    <t>0.7392,0.0572,0.2914,0.0049</t>
+  </si>
+  <si>
+    <t>0.8357,0.0184,0.2229,0.0073</t>
+  </si>
+  <si>
+    <t>0.8225,0.0156,0.2733,0.0029</t>
+  </si>
+  <si>
+    <t>0.8905,0.0192,0.1251,0.0036</t>
+  </si>
+  <si>
+    <t>0.7832,0.1708,0.0333,0.0065</t>
+  </si>
+  <si>
+    <t>0.7200,0.2296,0.0441,0.0144</t>
+  </si>
+  <si>
+    <t>0.6721,0.2635,0.0836,0.0158</t>
+  </si>
+  <si>
+    <t>0.5722,0.3984,0.0454,0.0143</t>
+  </si>
+  <si>
+    <t>0.5472,0.4491,0.0610,0.0105</t>
+  </si>
+  <si>
+    <t>0.5549,0.3843,0.0698,0.0216</t>
+  </si>
+  <si>
+    <t>0.6187,0.2748,0.0396,0.0179</t>
+  </si>
+  <si>
+    <t>0.7286,0.1910,0.1237,0.0146</t>
+  </si>
+  <si>
+    <t>0.5007,0.0354,0.5594,0.0023</t>
+  </si>
+  <si>
+    <t>0.1959,0.0196,0.8745,0.0012</t>
+  </si>
+  <si>
+    <t>0.5569,0.0189,0.6087,0.0042</t>
+  </si>
+  <si>
+    <t>0.3881,0.0455,0.6521,0.0025</t>
+  </si>
+  <si>
+    <t>0.1762,0.0058,0.9176,0.0008</t>
+  </si>
+  <si>
+    <t>0.7410,0.0108,0.3872,0.0043</t>
+  </si>
+  <si>
+    <t>0.8825,0.0171,0.1561,0.0023</t>
+  </si>
+  <si>
+    <t>0.8033,0.0060,0.3447,0.0022</t>
+  </si>
+  <si>
+    <t>0.8632,0.0386,0.0831,0.0096</t>
+  </si>
+  <si>
+    <t>0.7508,0.0262,0.3379,0.0098</t>
+  </si>
+  <si>
+    <t>0.8631,0.0342,0.0971,0.0145</t>
+  </si>
+  <si>
+    <t>0.7182,0.0870,0.1949,0.0668</t>
+  </si>
+  <si>
+    <t>0.6454,0.1182,0.2899,0.0762</t>
+  </si>
+  <si>
+    <t>0.7370,0.0899,0.1818,0.0129</t>
   </si>
 </sst>
 </file>
@@ -2051,7 +2051,7 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D9" t="s">
         <v>271</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3269,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D96" t="s">
         <v>358</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3689,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
         <v>388</v>
@@ -4473,7 +4473,7 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D182" t="s">
         <v>444</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4739,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
         <v>463</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5215,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D235" t="s">
         <v>497</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7556,0.0875,0.1822,0.0088</t>
-  </si>
-  <si>
-    <t>0.6782,0.1016,0.2964,0.0396</t>
-  </si>
-  <si>
-    <t>0.6053,0.2495,0.1656,0.0189</t>
-  </si>
-  <si>
-    <t>0.7961,0.0613,0.1111,0.0356</t>
-  </si>
-  <si>
-    <t>0.6247,0.2503,0.0648,0.0428</t>
-  </si>
-  <si>
-    <t>0.7779,0.1253,0.0330,0.0220</t>
-  </si>
-  <si>
-    <t>0.6902,0.2021,0.0898,0.0229</t>
-  </si>
-  <si>
-    <t>0.7128,0.2137,0.0418,0.0135</t>
-  </si>
-  <si>
-    <t>0.5937,0.3569,0.0749,0.0126</t>
-  </si>
-  <si>
-    <t>0.4814,0.4878,0.1098,0.0103</t>
-  </si>
-  <si>
-    <t>0.8214,0.0920,0.0286,0.0270</t>
-  </si>
-  <si>
-    <t>0.6986,0.2426,0.0393,0.0171</t>
-  </si>
-  <si>
-    <t>0.7860,0.0252,0.3023,0.0023</t>
-  </si>
-  <si>
-    <t>0.7821,0.0377,0.2400,0.0025</t>
-  </si>
-  <si>
-    <t>0.7506,0.0351,0.3154,0.0086</t>
-  </si>
-  <si>
-    <t>0.7667,0.0245,0.3356,0.0024</t>
-  </si>
-  <si>
-    <t>0.7226,0.1176,0.1585,0.0151</t>
-  </si>
-  <si>
-    <t>0.6357,0.2721,0.1051,0.0045</t>
-  </si>
-  <si>
-    <t>0.6464,0.2900,0.0761,0.0032</t>
-  </si>
-  <si>
-    <t>0.6377,0.2832,0.1075,0.0048</t>
-  </si>
-  <si>
-    <t>0.2399,0.6822,0.1075,0.0040</t>
-  </si>
-  <si>
-    <t>0.6173,0.3179,0.0606,0.0040</t>
-  </si>
-  <si>
-    <t>0.8585,0.0210,0.1816,0.0035</t>
-  </si>
-  <si>
-    <t>0.7347,0.0081,0.4433,0.0019</t>
-  </si>
-  <si>
-    <t>0.8392,0.0028,0.3401,0.0010</t>
-  </si>
-  <si>
-    <t>0.6510,0.0215,0.4651,0.0084</t>
-  </si>
-  <si>
-    <t>0.6755,0.0184,0.4488,0.0035</t>
-  </si>
-  <si>
-    <t>0.7303,0.0084,0.4641,0.0015</t>
-  </si>
-  <si>
-    <t>0.3512,0.0111,0.7956,0.0018</t>
-  </si>
-  <si>
-    <t>0.8273,0.0886,0.1020,0.0067</t>
-  </si>
-  <si>
-    <t>0.5998,0.2790,0.1025,0.0272</t>
-  </si>
-  <si>
-    <t>0.0386,0.2900,0.9465,0.0065</t>
-  </si>
-  <si>
-    <t>0.5388,0.1605,0.3086,0.0035</t>
-  </si>
-  <si>
-    <t>0.6139,0.2091,0.2036,0.0216</t>
-  </si>
-  <si>
-    <t>0.7230,0.1236,0.1803,0.0150</t>
-  </si>
-  <si>
-    <t>0.9091,0.0397,0.0127,0.0092</t>
-  </si>
-  <si>
-    <t>0.8303,0.0874,0.0918,0.0030</t>
-  </si>
-  <si>
-    <t>0.4344,0.0603,0.5149,0.0043</t>
-  </si>
-  <si>
-    <t>0.1708,0.0085,0.8979,0.0017</t>
-  </si>
-  <si>
-    <t>0.5338,0.0193,0.6206,0.0009</t>
-  </si>
-  <si>
-    <t>0.8003,0.0061,0.3338,0.0023</t>
-  </si>
-  <si>
-    <t>0.5293,0.0055,0.7125,0.0008</t>
-  </si>
-  <si>
-    <t>0.4340,0.0319,0.5294,0.0018</t>
-  </si>
-  <si>
-    <t>0.6776,0.0076,0.5118,0.0017</t>
-  </si>
-  <si>
-    <t>0.8634,0.0352,0.0886,0.0179</t>
-  </si>
-  <si>
-    <t>0.7734,0.0673,0.1500,0.0013</t>
-  </si>
-  <si>
-    <t>0.6084,0.0685,0.3356,0.0012</t>
-  </si>
-  <si>
-    <t>0.7039,0.2005,0.0730,0.0014</t>
-  </si>
-  <si>
-    <t>0.0356,0.0535,0.9580,0.0039</t>
-  </si>
-  <si>
-    <t>0.0736,0.0070,0.9674,0.0005</t>
-  </si>
-  <si>
-    <t>0.7806,0.0232,0.3318,0.0033</t>
-  </si>
-  <si>
-    <t>0.6990,0.0141,0.4807,0.0021</t>
-  </si>
-  <si>
-    <t>0.0490,0.0061,0.9710,0.0005</t>
-  </si>
-  <si>
-    <t>0.2742,0.0118,0.8542,0.0011</t>
-  </si>
-  <si>
-    <t>0.7716,0.1723,0.0343,0.0098</t>
-  </si>
-  <si>
-    <t>0.7712,0.1286,0.0322,0.0243</t>
-  </si>
-  <si>
-    <t>0.6465,0.2675,0.0600,0.0290</t>
-  </si>
-  <si>
-    <t>0.4222,0.2782,0.5133,0.0219</t>
-  </si>
-  <si>
-    <t>0.7295,0.1750,0.0464,0.0304</t>
-  </si>
-  <si>
-    <t>0.7124,0.2036,0.0310,0.0164</t>
-  </si>
-  <si>
-    <t>0.5393,0.3983,0.0450,0.0135</t>
-  </si>
-  <si>
-    <t>0.0249,0.1816,0.9527,0.0012</t>
-  </si>
-  <si>
-    <t>0.0713,0.0111,0.9635,0.0007</t>
-  </si>
-  <si>
-    <t>0.2494,0.0263,0.7922,0.0035</t>
-  </si>
-  <si>
-    <t>0.1165,0.0567,0.8902,0.0020</t>
-  </si>
-  <si>
-    <t>0.0468,0.0120,0.9728,0.0006</t>
-  </si>
-  <si>
-    <t>0.6143,0.1853,0.1587,0.0022</t>
-  </si>
-  <si>
-    <t>0.0309,0.9683,0.0064,0.0005</t>
-  </si>
-  <si>
-    <t>0.7087,0.1847,0.1392,0.0101</t>
-  </si>
-  <si>
-    <t>0.7484,0.1625,0.0934,0.0092</t>
-  </si>
-  <si>
-    <t>0.1708,0.3516,0.6884,0.0145</t>
-  </si>
-  <si>
-    <t>0.2638,0.0587,0.6817,0.0013</t>
-  </si>
-  <si>
-    <t>0.4688,0.0342,0.6319,0.0014</t>
-  </si>
-  <si>
-    <t>0.1139,0.3749,0.3380,0.0011</t>
-  </si>
-  <si>
-    <t>0.0944,0.1535,0.7773,0.0012</t>
-  </si>
-  <si>
-    <t>0.9029,0.0077,0.0482,0.0176</t>
-  </si>
-  <si>
-    <t>0.8326,0.0348,0.0768,0.0536</t>
-  </si>
-  <si>
-    <t>0.7595,0.0223,0.1742,0.0556</t>
-  </si>
-  <si>
-    <t>0.8692,0.0222,0.0718,0.0233</t>
-  </si>
-  <si>
-    <t>0.7715,0.0769,0.2178,0.0153</t>
-  </si>
-  <si>
-    <t>0.7877,0.0457,0.2086,0.0198</t>
-  </si>
-  <si>
-    <t>0.1404,0.0938,0.7670,0.0013</t>
-  </si>
-  <si>
-    <t>0.0295,0.0667,0.9667,0.0003</t>
-  </si>
-  <si>
-    <t>0.3307,0.0194,0.7825,0.0023</t>
-  </si>
-  <si>
-    <t>0.5174,0.0290,0.5973,0.0035</t>
-  </si>
-  <si>
-    <t>0.0668,0.3156,0.6229,0.0008</t>
-  </si>
-  <si>
-    <t>0.2865,0.0374,0.7313,0.0011</t>
-  </si>
-  <si>
-    <t>0.4306,0.4778,0.1444,0.0318</t>
-  </si>
-  <si>
-    <t>0.6054,0.3472,0.0696,0.0109</t>
-  </si>
-  <si>
-    <t>0.5634,0.4038,0.1016,0.0136</t>
-  </si>
-  <si>
-    <t>0.5589,0.3119,0.0930,0.0371</t>
-  </si>
-  <si>
-    <t>0.7955,0.1420,0.0278,0.0108</t>
-  </si>
-  <si>
-    <t>0.6126,0.2700,0.0414,0.0233</t>
-  </si>
-  <si>
-    <t>0.5217,0.4191,0.0788,0.0165</t>
-  </si>
-  <si>
-    <t>0.5262,0.4245,0.0906,0.0175</t>
-  </si>
-  <si>
-    <t>0.6102,0.2884,0.0584,0.0214</t>
-  </si>
-  <si>
-    <t>0.4712,0.4766,0.0866,0.0164</t>
-  </si>
-  <si>
-    <t>0.5944,0.3549,0.0766,0.0186</t>
-  </si>
-  <si>
-    <t>0.6392,0.2236,0.0343,0.0277</t>
-  </si>
-  <si>
-    <t>0.8525,0.0634,0.0202,0.0224</t>
-  </si>
-  <si>
-    <t>0.7159,0.2036,0.0445,0.0154</t>
-  </si>
-  <si>
-    <t>0.8093,0.1189,0.0199,0.0145</t>
-  </si>
-  <si>
-    <t>0.5683,0.3669,0.0787,0.0239</t>
-  </si>
-  <si>
-    <t>0.3247,0.0195,0.7758,0.0025</t>
-  </si>
-  <si>
-    <t>0.6748,0.0196,0.4653,0.0022</t>
-  </si>
-  <si>
-    <t>0.7257,0.0136,0.3956,0.0057</t>
-  </si>
-  <si>
-    <t>0.4528,0.0153,0.7004,0.0030</t>
-  </si>
-  <si>
-    <t>0.2594,0.6177,0.1726,0.0082</t>
-  </si>
-  <si>
-    <t>0.6026,0.3697,0.0699,0.0075</t>
-  </si>
-  <si>
-    <t>0.7877,0.1598,0.0673,0.0050</t>
-  </si>
-  <si>
-    <t>0.5178,0.4538,0.0987,0.0065</t>
-  </si>
-  <si>
-    <t>0.4724,0.4832,0.0999,0.0141</t>
-  </si>
-  <si>
-    <t>0.2983,0.6490,0.1070,0.0058</t>
-  </si>
-  <si>
-    <t>0.6415,0.2994,0.0971,0.0112</t>
-  </si>
-  <si>
-    <t>0.7872,0.0498,0.1980,0.0114</t>
-  </si>
-  <si>
-    <t>0.7747,0.0498,0.2309,0.0073</t>
-  </si>
-  <si>
-    <t>0.8249,0.0306,0.2277,0.0058</t>
-  </si>
-  <si>
-    <t>0.7685,0.0476,0.2651,0.0069</t>
-  </si>
-  <si>
-    <t>0.7916,0.0653,0.1512,0.0113</t>
-  </si>
-  <si>
-    <t>0.5203,0.3064,0.1475,0.0051</t>
-  </si>
-  <si>
-    <t>0.3779,0.3655,0.1818,0.0029</t>
-  </si>
-  <si>
-    <t>0.6637,0.2158,0.1200,0.0090</t>
-  </si>
-  <si>
-    <t>0.1433,0.6795,0.1775,0.0019</t>
-  </si>
-  <si>
-    <t>0.4560,0.4542,0.1159,0.0031</t>
-  </si>
-  <si>
-    <t>0.7111,0.2269,0.0406,0.0082</t>
-  </si>
-  <si>
-    <t>0.4988,0.4334,0.1159,0.0150</t>
-  </si>
-  <si>
-    <t>0.7757,0.1322,0.0395,0.0181</t>
-  </si>
-  <si>
-    <t>0.7893,0.0936,0.0257,0.0262</t>
-  </si>
-  <si>
-    <t>0.6824,0.2056,0.0758,0.0305</t>
-  </si>
-  <si>
-    <t>0.4880,0.4374,0.1381,0.0137</t>
-  </si>
-  <si>
-    <t>0.7441,0.2076,0.0371,0.0146</t>
-  </si>
-  <si>
-    <t>0.7992,0.1308,0.0881,0.0100</t>
-  </si>
-  <si>
-    <t>0.7587,0.1164,0.0293,0.0326</t>
-  </si>
-  <si>
-    <t>0.6966,0.2033,0.0317,0.0229</t>
-  </si>
-  <si>
-    <t>0.3465,0.0086,0.8082,0.0014</t>
-  </si>
-  <si>
-    <t>0.4475,0.0096,0.7381,0.0009</t>
-  </si>
-  <si>
-    <t>0.1437,0.0055,0.9256,0.0012</t>
-  </si>
-  <si>
-    <t>0.5428,0.0269,0.5696,0.0016</t>
-  </si>
-  <si>
-    <t>0.8382,0.0381,0.1556,0.0048</t>
-  </si>
-  <si>
-    <t>0.7868,0.0380,0.2740,0.0072</t>
-  </si>
-  <si>
-    <t>0.7220,0.0645,0.2919,0.0114</t>
-  </si>
-  <si>
-    <t>0.8839,0.0269,0.0838,0.0074</t>
-  </si>
-  <si>
-    <t>0.8230,0.0428,0.0986,0.0328</t>
-  </si>
-  <si>
-    <t>0.7218,0.0197,0.1913,0.0673</t>
-  </si>
-  <si>
-    <t>0.8418,0.0171,0.1064,0.0337</t>
-  </si>
-  <si>
-    <t>0.8539,0.0142,0.0895,0.0297</t>
-  </si>
-  <si>
-    <t>0.2053,0.1595,0.6235,0.0042</t>
-  </si>
-  <si>
-    <t>0.7742,0.1419,0.0369,0.0140</t>
-  </si>
-  <si>
-    <t>0.8620,0.0574,0.0306,0.0126</t>
-  </si>
-  <si>
-    <t>0.7019,0.2413,0.0487,0.0160</t>
-  </si>
-  <si>
-    <t>0.7483,0.1734,0.0925,0.0184</t>
-  </si>
-  <si>
-    <t>0.5698,0.3473,0.1355,0.0186</t>
-  </si>
-  <si>
-    <t>0.7112,0.1634,0.0955,0.0164</t>
-  </si>
-  <si>
-    <t>0.7323,0.1424,0.1003,0.0362</t>
-  </si>
-  <si>
-    <t>0.0962,0.0480,0.8964,0.0183</t>
-  </si>
-  <si>
-    <t>0.7790,0.0818,0.0873,0.0270</t>
-  </si>
-  <si>
-    <t>0.7251,0.1892,0.0562,0.0209</t>
-  </si>
-  <si>
-    <t>0.8274,0.0688,0.1059,0.0049</t>
-  </si>
-  <si>
-    <t>0.8106,0.0702,0.1179,0.0104</t>
-  </si>
-  <si>
-    <t>0.6443,0.2587,0.1295,0.0075</t>
-  </si>
-  <si>
-    <t>0.7971,0.0550,0.2091,0.0085</t>
-  </si>
-  <si>
-    <t>0.8040,0.1252,0.0746,0.0040</t>
-  </si>
-  <si>
-    <t>0.8728,0.0985,0.0235,0.0042</t>
-  </si>
-  <si>
-    <t>0.6635,0.2383,0.1272,0.0199</t>
-  </si>
-  <si>
-    <t>0.6178,0.2493,0.1026,0.0322</t>
-  </si>
-  <si>
-    <t>0.5693,0.3328,0.0640,0.0190</t>
-  </si>
-  <si>
-    <t>0.7613,0.1356,0.0236,0.0203</t>
-  </si>
-  <si>
-    <t>0.6545,0.2884,0.1082,0.0237</t>
-  </si>
-  <si>
-    <t>0.7412,0.1754,0.0343,0.0209</t>
-  </si>
-  <si>
-    <t>0.9438,0.0243,0.0079,0.0053</t>
-  </si>
-  <si>
-    <t>0.7484,0.1458,0.0522,0.0324</t>
-  </si>
-  <si>
-    <t>0.6860,0.2350,0.0772,0.0115</t>
-  </si>
-  <si>
-    <t>0.5377,0.4279,0.1147,0.0126</t>
-  </si>
-  <si>
-    <t>0.5410,0.4007,0.0869,0.0125</t>
-  </si>
-  <si>
-    <t>0.6756,0.1889,0.1710,0.0150</t>
-  </si>
-  <si>
-    <t>0.5904,0.3753,0.0803,0.0091</t>
-  </si>
-  <si>
-    <t>0.6926,0.1977,0.1113,0.0210</t>
-  </si>
-  <si>
-    <t>0.6232,0.3365,0.0450,0.0119</t>
-  </si>
-  <si>
-    <t>0.6397,0.2477,0.0616,0.0159</t>
-  </si>
-  <si>
-    <t>0.0188,0.2041,0.9518,0.0017</t>
-  </si>
-  <si>
-    <t>0.3567,0.5517,0.1943,0.0152</t>
-  </si>
-  <si>
-    <t>0.4077,0.0136,0.7196,0.0026</t>
-  </si>
-  <si>
-    <t>0.6671,0.0176,0.4821,0.0050</t>
-  </si>
-  <si>
-    <t>0.4085,0.0484,0.6494,0.0035</t>
-  </si>
-  <si>
-    <t>0.0190,0.0168,0.9913,0.0004</t>
-  </si>
-  <si>
-    <t>0.5465,0.0189,0.6198,0.0032</t>
-  </si>
-  <si>
-    <t>0.6367,0.0062,0.5713,0.0015</t>
-  </si>
-  <si>
-    <t>0.2423,0.0180,0.8398,0.0016</t>
-  </si>
-  <si>
-    <t>0.6939,0.0490,0.3685,0.0107</t>
-  </si>
-  <si>
-    <t>0.7122,0.0354,0.3738,0.0049</t>
-  </si>
-  <si>
-    <t>0.8078,0.0882,0.0979,0.0033</t>
-  </si>
-  <si>
-    <t>0.5420,0.1782,0.3228,0.0086</t>
-  </si>
-  <si>
-    <t>0.7297,0.0519,0.3069,0.0078</t>
-  </si>
-  <si>
-    <t>0.7992,0.0308,0.2659,0.0045</t>
-  </si>
-  <si>
-    <t>0.7938,0.0479,0.1974,0.0094</t>
-  </si>
-  <si>
-    <t>0.7954,0.0501,0.1844,0.0068</t>
-  </si>
-  <si>
-    <t>0.6204,0.3349,0.0624,0.0061</t>
-  </si>
-  <si>
-    <t>0.6479,0.3073,0.0850,0.0090</t>
-  </si>
-  <si>
-    <t>0.5336,0.3701,0.1259,0.0261</t>
-  </si>
-  <si>
-    <t>0.6829,0.2277,0.0449,0.0174</t>
-  </si>
-  <si>
-    <t>0.7422,0.2126,0.0324,0.0094</t>
-  </si>
-  <si>
-    <t>0.8166,0.0573,0.1390,0.0057</t>
-  </si>
-  <si>
-    <t>0.8269,0.0331,0.1763,0.0041</t>
-  </si>
-  <si>
-    <t>0.8561,0.0307,0.1417,0.0046</t>
-  </si>
-  <si>
-    <t>0.8903,0.0133,0.1336,0.0040</t>
-  </si>
-  <si>
-    <t>0.7985,0.0393,0.2076,0.0226</t>
-  </si>
-  <si>
-    <t>0.0803,0.0500,0.9366,0.0030</t>
-  </si>
-  <si>
-    <t>0.8206,0.0056,0.3152,0.0029</t>
-  </si>
-  <si>
-    <t>0.8425,0.0072,0.2787,0.0026</t>
-  </si>
-  <si>
-    <t>0.5820,0.0125,0.5099,0.0074</t>
-  </si>
-  <si>
-    <t>0.6409,0.0111,0.5195,0.0022</t>
-  </si>
-  <si>
-    <t>0.4916,0.4646,0.0831,0.0199</t>
-  </si>
-  <si>
-    <t>0.4553,0.4966,0.0917,0.0161</t>
-  </si>
-  <si>
-    <t>0.8036,0.1317,0.0618,0.0147</t>
-  </si>
-  <si>
-    <t>0.5614,0.3726,0.0517,0.0207</t>
-  </si>
-  <si>
-    <t>0.6101,0.3063,0.0564,0.0211</t>
-  </si>
-  <si>
-    <t>0.7473,0.1821,0.0214,0.0207</t>
-  </si>
-  <si>
-    <t>0.5574,0.4118,0.0502,0.0113</t>
-  </si>
-  <si>
-    <t>0.6465,0.2550,0.0442,0.0142</t>
-  </si>
-  <si>
-    <t>0.6348,0.0946,0.3651,0.0095</t>
-  </si>
-  <si>
-    <t>0.6791,0.2142,0.1213,0.0061</t>
-  </si>
-  <si>
-    <t>0.6528,0.2668,0.1322,0.0146</t>
-  </si>
-  <si>
-    <t>0.0398,0.0074,0.9801,0.0006</t>
-  </si>
-  <si>
-    <t>0.0223,0.0078,0.9820,0.0014</t>
-  </si>
-  <si>
-    <t>0.5155,0.0165,0.6322,0.0029</t>
-  </si>
-  <si>
-    <t>0.0461,0.0101,0.9723,0.0012</t>
-  </si>
-  <si>
-    <t>0.2712,0.0102,0.8503,0.0011</t>
-  </si>
-  <si>
-    <t>0.0067,0.0082,0.9936,0.0007</t>
-  </si>
-  <si>
-    <t>0.3699,0.0152,0.7833,0.0016</t>
-  </si>
-  <si>
-    <t>0.7392,0.0572,0.2914,0.0049</t>
-  </si>
-  <si>
-    <t>0.8357,0.0184,0.2229,0.0073</t>
-  </si>
-  <si>
-    <t>0.8225,0.0156,0.2733,0.0029</t>
-  </si>
-  <si>
-    <t>0.8905,0.0192,0.1251,0.0036</t>
-  </si>
-  <si>
-    <t>0.7832,0.1708,0.0333,0.0065</t>
-  </si>
-  <si>
-    <t>0.7200,0.2296,0.0441,0.0144</t>
-  </si>
-  <si>
-    <t>0.6721,0.2635,0.0836,0.0158</t>
-  </si>
-  <si>
-    <t>0.5722,0.3984,0.0454,0.0143</t>
-  </si>
-  <si>
-    <t>0.5472,0.4491,0.0610,0.0105</t>
-  </si>
-  <si>
-    <t>0.5549,0.3843,0.0698,0.0216</t>
-  </si>
-  <si>
-    <t>0.6187,0.2748,0.0396,0.0179</t>
-  </si>
-  <si>
-    <t>0.7286,0.1910,0.1237,0.0146</t>
-  </si>
-  <si>
-    <t>0.5007,0.0354,0.5594,0.0023</t>
-  </si>
-  <si>
-    <t>0.1959,0.0196,0.8745,0.0012</t>
-  </si>
-  <si>
-    <t>0.5569,0.0189,0.6087,0.0042</t>
-  </si>
-  <si>
-    <t>0.3881,0.0455,0.6521,0.0025</t>
-  </si>
-  <si>
-    <t>0.1762,0.0058,0.9176,0.0008</t>
-  </si>
-  <si>
-    <t>0.7410,0.0108,0.3872,0.0043</t>
-  </si>
-  <si>
-    <t>0.8825,0.0171,0.1561,0.0023</t>
-  </si>
-  <si>
-    <t>0.8033,0.0060,0.3447,0.0022</t>
-  </si>
-  <si>
-    <t>0.8632,0.0386,0.0831,0.0096</t>
-  </si>
-  <si>
-    <t>0.7508,0.0262,0.3379,0.0098</t>
-  </si>
-  <si>
-    <t>0.8631,0.0342,0.0971,0.0145</t>
-  </si>
-  <si>
-    <t>0.7182,0.0870,0.1949,0.0668</t>
-  </si>
-  <si>
-    <t>0.6454,0.1182,0.2899,0.0762</t>
-  </si>
-  <si>
-    <t>0.7370,0.0899,0.1818,0.0129</t>
+    <t>0.9576,0.0020,0.0078,0.0177</t>
+  </si>
+  <si>
+    <t>0.1685,0.0010,0.0044,0.9171</t>
+  </si>
+  <si>
+    <t>0.9496,0.0037,0.0137,0.0152</t>
+  </si>
+  <si>
+    <t>0.5450,0.0042,0.0115,0.5553</t>
+  </si>
+  <si>
+    <t>0.9974,0.0017,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0027,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0033,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9893,0.0063,0.0013,0.0016</t>
+  </si>
+  <si>
+    <t>0.9954,0.0022,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9936,0.0045,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9954,0.0029,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0020,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.8725,0.0067,0.2332,0.0010</t>
+  </si>
+  <si>
+    <t>0.4864,0.0027,0.7518,0.0007</t>
+  </si>
+  <si>
+    <t>0.6242,0.0040,0.6438,0.0006</t>
+  </si>
+  <si>
+    <t>0.0963,0.0066,0.9456,0.0007</t>
+  </si>
+  <si>
+    <t>0.9343,0.0026,0.1510,0.0005</t>
+  </si>
+  <si>
+    <t>0.0272,0.9675,0.0114,0.0006</t>
+  </si>
+  <si>
+    <t>0.0464,0.9485,0.0166,0.0015</t>
+  </si>
+  <si>
+    <t>0.0500,0.9123,0.1035,0.0014</t>
+  </si>
+  <si>
+    <t>0.0422,0.9605,0.0082,0.0012</t>
+  </si>
+  <si>
+    <t>0.0033,0.9910,0.0147,0.0008</t>
+  </si>
+  <si>
+    <t>0.7282,0.0049,0.4591,0.0018</t>
+  </si>
+  <si>
+    <t>0.4929,0.0010,0.6435,0.0022</t>
+  </si>
+  <si>
+    <t>0.0183,0.0016,0.9877,0.0006</t>
+  </si>
+  <si>
+    <t>0.1622,0.0030,0.9208,0.0006</t>
+  </si>
+  <si>
+    <t>0.0197,0.0040,0.9902,0.0003</t>
+  </si>
+  <si>
+    <t>0.3150,0.0039,0.8012,0.0034</t>
+  </si>
+  <si>
+    <t>0.0032,0.0007,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.2225,0.7648,0.0532,0.0029</t>
+  </si>
+  <si>
+    <t>0.2053,0.0853,0.8361,0.0020</t>
+  </si>
+  <si>
+    <t>0.0008,0.0049,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0245,0.3179,0.7599,0.0003</t>
+  </si>
+  <si>
+    <t>0.7972,0.1045,0.1856,0.0153</t>
+  </si>
+  <si>
+    <t>0.8268,0.0617,0.1610,0.0028</t>
+  </si>
+  <si>
+    <t>0.5761,0.3874,0.0412,0.0008</t>
+  </si>
+  <si>
+    <t>0.0189,0.9250,0.4220,0.0015</t>
+  </si>
+  <si>
+    <t>0.0095,0.1009,0.9667,0.0055</t>
+  </si>
+  <si>
+    <t>0.0485,0.0140,0.9522,0.0034</t>
+  </si>
+  <si>
+    <t>0.0975,0.0108,0.9291,0.0017</t>
+  </si>
+  <si>
+    <t>0.0833,0.0062,0.8804,0.0241</t>
+  </si>
+  <si>
+    <t>0.0527,0.0982,0.9397,0.0018</t>
+  </si>
+  <si>
+    <t>0.0848,0.6231,0.1443,0.0023</t>
+  </si>
+  <si>
+    <t>0.0181,0.0041,0.9893,0.0003</t>
+  </si>
+  <si>
+    <t>0.7343,0.0536,0.2365,0.0567</t>
+  </si>
+  <si>
+    <t>0.0050,0.9813,0.0126,0.0100</t>
+  </si>
+  <si>
+    <t>0.0352,0.9141,0.1517,0.0101</t>
+  </si>
+  <si>
+    <t>0.0074,0.9712,0.2793,0.0017</t>
+  </si>
+  <si>
+    <t>0.0009,0.0033,0.9980,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.0015,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.0321,0.0032,0.9757,0.0013</t>
+  </si>
+  <si>
+    <t>0.0223,0.0035,0.9828,0.0011</t>
+  </si>
+  <si>
+    <t>0.0013,0.0012,0.9978,0.0006</t>
+  </si>
+  <si>
+    <t>0.0014,0.0012,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.9586,0.0771,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.9875,0.0054,0.0069,0.0010</t>
+  </si>
+  <si>
+    <t>0.9921,0.0051,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.0049,0.0517,0.9955,0.0004</t>
+  </si>
+  <si>
+    <t>0.9801,0.0128,0.0058,0.0014</t>
+  </si>
+  <si>
+    <t>0.9968,0.0018,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9704,0.0509,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.6094,0.9967,0.0004</t>
+  </si>
+  <si>
+    <t>0.0036,0.0049,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.0032,0.0019,0.9963,0.0006</t>
+  </si>
+  <si>
+    <t>0.0017,0.9791,0.6052,0.0013</t>
+  </si>
+  <si>
+    <t>0.0005,0.0020,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0617,0.8664,0.1180,0.0015</t>
+  </si>
+  <si>
+    <t>0.0066,0.9918,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.4447,0.0367,0.7186,0.0046</t>
+  </si>
+  <si>
+    <t>0.3805,0.1514,0.5509,0.0031</t>
+  </si>
+  <si>
+    <t>0.0037,0.0419,0.9941,0.0020</t>
+  </si>
+  <si>
+    <t>0.0034,0.6338,0.9545,0.0006</t>
+  </si>
+  <si>
+    <t>0.0032,0.4615,0.9712,0.0013</t>
+  </si>
+  <si>
+    <t>0.0008,0.9834,0.6690,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.9020,0.9233,0.0007</t>
+  </si>
+  <si>
+    <t>0.1351,0.0017,0.0257,0.8575</t>
+  </si>
+  <si>
+    <t>0.0206,0.0008,0.0035,0.9878</t>
+  </si>
+  <si>
+    <t>0.0110,0.0027,0.0168,0.9835</t>
+  </si>
+  <si>
+    <t>0.2757,0.0028,0.0540,0.6335</t>
+  </si>
+  <si>
+    <t>0.0403,0.0010,0.0080,0.9704</t>
+  </si>
+  <si>
+    <t>0.1925,0.0028,0.0163,0.8466</t>
+  </si>
+  <si>
+    <t>0.0016,0.8652,0.9627,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.6209,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.3268,0.9792,0.0010</t>
+  </si>
+  <si>
+    <t>0.0031,0.3823,0.9793,0.0010</t>
+  </si>
+  <si>
+    <t>0.0015,0.8914,0.9069,0.0003</t>
+  </si>
+  <si>
+    <t>0.0111,0.2308,0.9029,0.0015</t>
+  </si>
+  <si>
+    <t>0.9927,0.0043,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9858,0.0217,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9652,0.0596,0.0037,0.0006</t>
+  </si>
+  <si>
+    <t>0.9797,0.0116,0.0016,0.0023</t>
+  </si>
+  <si>
+    <t>0.9861,0.0091,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.9945,0.0044,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9943,0.0056,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9902,0.0093,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9929,0.0064,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0049,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0012,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0020,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9949,0.0036,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9954,0.0034,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9949,0.0034,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0009,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0091,0.0021,0.9936,0.0003</t>
+  </si>
+  <si>
+    <t>0.9679,0.0012,0.0642,0.0004</t>
+  </si>
+  <si>
+    <t>0.2595,0.0020,0.8681,0.0007</t>
+  </si>
+  <si>
+    <t>0.0055,0.9907,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.0050,0.9896,0.0125,0.0005</t>
+  </si>
+  <si>
+    <t>0.1175,0.9130,0.0092,0.0019</t>
+  </si>
+  <si>
+    <t>0.1660,0.8490,0.0324,0.0056</t>
+  </si>
+  <si>
+    <t>0.0272,0.9580,0.0274,0.0013</t>
+  </si>
+  <si>
+    <t>0.0018,0.9949,0.0053,0.0004</t>
+  </si>
+  <si>
+    <t>0.6637,0.3936,0.0225,0.0010</t>
+  </si>
+  <si>
+    <t>0.6111,0.0223,0.5116,0.0047</t>
+  </si>
+  <si>
+    <t>0.3808,0.0039,0.8047,0.0009</t>
+  </si>
+  <si>
+    <t>0.6532,0.0542,0.3615,0.0082</t>
+  </si>
+  <si>
+    <t>0.5974,0.0140,0.5587,0.0026</t>
+  </si>
+  <si>
+    <t>0.2291,0.0496,0.7364,0.0719</t>
+  </si>
+  <si>
+    <t>0.0052,0.9860,0.0211,0.0017</t>
+  </si>
+  <si>
+    <t>0.0091,0.9770,0.0202,0.0042</t>
+  </si>
+  <si>
+    <t>0.0398,0.9366,0.0420,0.0040</t>
+  </si>
+  <si>
+    <t>0.0138,0.9583,0.1084,0.0049</t>
+  </si>
+  <si>
+    <t>0.0136,0.9735,0.0401,0.0004</t>
+  </si>
+  <si>
+    <t>0.7759,0.3406,0.0109,0.0011</t>
+  </si>
+  <si>
+    <t>0.8781,0.1672,0.0162,0.0010</t>
+  </si>
+  <si>
+    <t>0.8962,0.1241,0.0123,0.0042</t>
+  </si>
+  <si>
+    <t>0.9957,0.0019,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0013,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9907,0.0041,0.0040,0.0005</t>
+  </si>
+  <si>
+    <t>0.9956,0.0016,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.9886,0.0109,0.0041,0.0005</t>
+  </si>
+  <si>
+    <t>0.9938,0.0016,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9965,0.0018,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0182,0.0889,0.9694,0.0015</t>
+  </si>
+  <si>
+    <t>0.0018,0.0561,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0066,0.0040,0.9924,0.0005</t>
+  </si>
+  <si>
+    <t>0.0118,0.0106,0.9858,0.0008</t>
+  </si>
+  <si>
+    <t>0.9715,0.0043,0.0408,0.0006</t>
+  </si>
+  <si>
+    <t>0.3829,0.0102,0.7408,0.0021</t>
+  </si>
+  <si>
+    <t>0.7054,0.0022,0.5204,0.0012</t>
+  </si>
+  <si>
+    <t>0.9096,0.0060,0.1559,0.0019</t>
+  </si>
+  <si>
+    <t>0.7605,0.0024,0.0280,0.1339</t>
+  </si>
+  <si>
+    <t>0.0031,0.0021,0.0166,0.9919</t>
+  </si>
+  <si>
+    <t>0.0103,0.0113,0.0237,0.9810</t>
+  </si>
+  <si>
+    <t>0.0659,0.0005,0.0087,0.9497</t>
+  </si>
+  <si>
+    <t>0.0030,0.9174,0.8629,0.0014</t>
+  </si>
+  <si>
+    <t>0.9967,0.0012,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.3912,0.6108,0.0509,0.0051</t>
+  </si>
+  <si>
+    <t>0.9952,0.0020,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.3563,0.6861,0.0231,0.0010</t>
+  </si>
+  <si>
+    <t>0.9831,0.0026,0.0055,0.0026</t>
+  </si>
+  <si>
+    <t>0.6606,0.0119,0.3725,0.0294</t>
+  </si>
+  <si>
+    <t>0.9938,0.0015,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.0100,0.0270,0.9788,0.0171</t>
+  </si>
+  <si>
+    <t>0.9558,0.0025,0.0300,0.0070</t>
+  </si>
+  <si>
+    <t>0.9780,0.0023,0.0009,0.0108</t>
+  </si>
+  <si>
+    <t>0.6203,0.1768,0.2232,0.0068</t>
+  </si>
+  <si>
+    <t>0.9394,0.0313,0.0271,0.0036</t>
+  </si>
+  <si>
+    <t>0.9632,0.0121,0.0382,0.0009</t>
+  </si>
+  <si>
+    <t>0.8321,0.0774,0.1275,0.0072</t>
+  </si>
+  <si>
+    <t>0.7846,0.1510,0.0624,0.0032</t>
+  </si>
+  <si>
+    <t>0.9534,0.0105,0.0569,0.0007</t>
+  </si>
+  <si>
+    <t>0.9951,0.0028,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9943,0.0034,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9955,0.0024,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9956,0.0019,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.9943,0.0021,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9941,0.0040,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9961,0.0008,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.7281,0.2902,0.0601,0.0059</t>
+  </si>
+  <si>
+    <t>0.6934,0.4198,0.0093,0.0007</t>
+  </si>
+  <si>
+    <t>0.5369,0.4527,0.0681,0.0043</t>
+  </si>
+  <si>
+    <t>0.1272,0.3114,0.7542,0.0046</t>
+  </si>
+  <si>
+    <t>0.9871,0.0213,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9657,0.0193,0.0173,0.0016</t>
+  </si>
+  <si>
+    <t>0.9902,0.0123,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.7215,0.4263,0.0077,0.0022</t>
+  </si>
+  <si>
+    <t>0.0004,0.0020,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9709,0.0191,0.0159,0.0012</t>
+  </si>
+  <si>
+    <t>0.0020,0.0005,0.9975,0.0003</t>
+  </si>
+  <si>
+    <t>0.0041,0.0465,0.9916,0.0008</t>
+  </si>
+  <si>
+    <t>0.0906,0.0060,0.9560,0.0008</t>
+  </si>
+  <si>
+    <t>0.0014,0.0914,0.9978,0.0003</t>
+  </si>
+  <si>
+    <t>0.0053,0.0014,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.0004,0.9982,0.0003</t>
+  </si>
+  <si>
+    <t>0.0068,0.0045,0.9946,0.0005</t>
+  </si>
+  <si>
+    <t>0.3092,0.0091,0.8230,0.0017</t>
+  </si>
+  <si>
+    <t>0.4413,0.0197,0.6801,0.0020</t>
+  </si>
+  <si>
+    <t>0.8399,0.0291,0.1886,0.0033</t>
+  </si>
+  <si>
+    <t>0.3916,0.0639,0.5388,0.0017</t>
+  </si>
+  <si>
+    <t>0.0963,0.4926,0.3899,0.0030</t>
+  </si>
+  <si>
+    <t>0.5387,0.0047,0.6883,0.0006</t>
+  </si>
+  <si>
+    <t>0.5818,0.0315,0.5269,0.0054</t>
+  </si>
+  <si>
+    <t>0.4825,0.0351,0.6184,0.0043</t>
+  </si>
+  <si>
+    <t>0.1933,0.8879,0.0062,0.0021</t>
+  </si>
+  <si>
+    <t>0.0742,0.9515,0.0038,0.0005</t>
+  </si>
+  <si>
+    <t>0.3578,0.7848,0.0061,0.0017</t>
+  </si>
+  <si>
+    <t>0.9880,0.0214,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9834,0.0335,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.6853,0.0180,0.4275,0.0026</t>
+  </si>
+  <si>
+    <t>0.9672,0.0016,0.0617,0.0004</t>
+  </si>
+  <si>
+    <t>0.8368,0.0304,0.1354,0.0167</t>
+  </si>
+  <si>
+    <t>0.8589,0.0018,0.3541,0.0004</t>
+  </si>
+  <si>
+    <t>0.5536,0.0066,0.5781,0.0049</t>
+  </si>
+  <si>
+    <t>0.0027,0.0017,0.9968,0.0007</t>
+  </si>
+  <si>
+    <t>0.0071,0.0068,0.9825,0.0048</t>
+  </si>
+  <si>
+    <t>0.0145,0.0288,0.9782,0.0023</t>
+  </si>
+  <si>
+    <t>0.0794,0.0104,0.9465,0.0011</t>
+  </si>
+  <si>
+    <t>0.0055,0.0393,0.9844,0.0011</t>
+  </si>
+  <si>
+    <t>0.9903,0.0092,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9933,0.0038,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9852,0.0162,0.0023,0.0008</t>
+  </si>
+  <si>
+    <t>0.9958,0.0033,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9894,0.0143,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9918,0.0083,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0011,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0072,0.0374,0.9928,0.0004</t>
+  </si>
+  <si>
+    <t>0.2238,0.4032,0.2708,0.0011</t>
+  </si>
+  <si>
+    <t>0.9509,0.0035,0.0797,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.0008,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0019,0.9988,0.0011</t>
+  </si>
+  <si>
+    <t>0.0022,0.0071,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0061,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.0159,0.0052,0.9858,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0129,0.0065,0.9831,0.0025</t>
+  </si>
+  <si>
+    <t>0.0386,0.0160,0.9727,0.0008</t>
+  </si>
+  <si>
+    <t>0.9066,0.0021,0.0510,0.0208</t>
+  </si>
+  <si>
+    <t>0.7171,0.0025,0.5357,0.0007</t>
+  </si>
+  <si>
+    <t>0.9479,0.0010,0.1245,0.0005</t>
+  </si>
+  <si>
+    <t>0.9899,0.0110,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0040,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0017,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9886,0.0103,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9964,0.0028,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9920,0.0079,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9784,0.0206,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9939,0.0060,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0441,0.0391,0.9340,0.0013</t>
+  </si>
+  <si>
+    <t>0.0023,0.0031,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.0129,0.0107,0.9852,0.0016</t>
+  </si>
+  <si>
+    <t>0.0539,0.0043,0.9705,0.0007</t>
+  </si>
+  <si>
+    <t>0.0129,0.0007,0.9929,0.0002</t>
+  </si>
+  <si>
+    <t>0.0556,0.0026,0.9428,0.0052</t>
+  </si>
+  <si>
+    <t>0.0840,0.0057,0.9368,0.0032</t>
+  </si>
+  <si>
+    <t>0.0310,0.0051,0.9704,0.0021</t>
+  </si>
+  <si>
+    <t>0.9657,0.0044,0.0044,0.0116</t>
+  </si>
+  <si>
+    <t>0.7149,0.0108,0.1276,0.1128</t>
+  </si>
+  <si>
+    <t>0.4050,0.0050,0.0387,0.5409</t>
+  </si>
+  <si>
+    <t>0.0058,0.0008,0.0100,0.9915</t>
+  </si>
+  <si>
+    <t>0.0438,0.0012,0.0049,0.9758</t>
+  </si>
+  <si>
+    <t>0.9730,0.0039,0.0288,0.0020</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2905,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3549,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
         <v>378</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3899,7 +3899,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
         <v>403</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4473,7 +4473,7 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D182" t="s">
         <v>444</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
         <v>495</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
